--- a/data/trans_camb/MCS12_SP_R2-Edad-trans_camb.xlsx
+++ b/data/trans_camb/MCS12_SP_R2-Edad-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud mental (SF12)</t>
+          <t>Población por debajo de la mediana (53.579) de la puntuación del componente de salud mental (SF12)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 8,8</t>
+          <t>-3,02; 8,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 7,53</t>
+          <t>-4,88; 8,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,51; 2,93</t>
+          <t>-14,83; 2,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 12,24</t>
+          <t>-0,22; 13,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 7,62</t>
+          <t>-6,44; 7,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,72; 4,99</t>
+          <t>-12,18; 4,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 9,1</t>
+          <t>0,11; 9,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 5,53</t>
+          <t>-3,75; 5,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 0,79</t>
+          <t>-12,43; 0,58</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 30,54</t>
+          <t>-8,82; 29,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-14,79; 25,47</t>
+          <t>-13,67; 26,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-42,58; 10,11</t>
+          <t>-43,9; 9,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 30,3</t>
+          <t>-0,51; 32,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-10,33; 19,08</t>
+          <t>-13,89; 18,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-28,66; 12,7</t>
+          <t>-27,69; 11,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 25,64</t>
+          <t>-0,08; 26,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 15,46</t>
+          <t>-9,44; 15,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-30,03; 2,57</t>
+          <t>-31,78; 1,67</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,11; 14,8</t>
+          <t>4,91; 15,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,03; 16,69</t>
+          <t>5,67; 16,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 6,41</t>
+          <t>-7,87; 5,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 12,83</t>
+          <t>1,04; 12,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 6,33</t>
+          <t>-4,95; 6,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,29; 19,65</t>
+          <t>-11,33; 18,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,05; 13,21</t>
+          <t>4,7; 12,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,48; 10,47</t>
+          <t>2,71; 10,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 14,14</t>
+          <t>-5,84; 15,93</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,55; 45,97</t>
+          <t>13,6; 47,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,21; 51,63</t>
+          <t>15,72; 53,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-20,78; 19,65</t>
+          <t>-21,79; 18,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,98; 28,25</t>
+          <t>2,08; 28,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-10,57; 13,95</t>
+          <t>-9,59; 14,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-23,0; 40,34</t>
+          <t>-23,02; 39,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,87; 33,87</t>
+          <t>11,07; 31,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,16; 26,64</t>
+          <t>6,23; 26,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-15,07; 35,98</t>
+          <t>-14,17; 40,16</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,24; 12,61</t>
+          <t>1,38; 12,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 10,11</t>
+          <t>-1,24; 9,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,08; -1,55</t>
+          <t>-12,85; -1,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,02; 10,95</t>
+          <t>0,3; 10,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,18; -2,93</t>
+          <t>-14,31; -3,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,8; -8,99</t>
+          <t>-19,65; -9,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,24; 10,25</t>
+          <t>2,37; 10,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 1,56</t>
+          <t>-6,15; 1,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-15,16; -7,12</t>
+          <t>-14,89; -7,04</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,62; 31,7</t>
+          <t>2,98; 32,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 24,87</t>
+          <t>-2,72; 23,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-28,33; -3,73</t>
+          <t>-28,43; -4,48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 19,44</t>
+          <t>0,46; 19,52</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-23,5; -5,18</t>
+          <t>-23,57; -5,95</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-31,21; -16,34</t>
+          <t>-31,76; -16,08</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,17; 20,69</t>
+          <t>4,25; 20,89</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-12,26; 3,16</t>
+          <t>-11,6; 3,17</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-28,39; -14,37</t>
+          <t>-28,01; -14,28</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,4; 14,22</t>
+          <t>2,06; 15,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,38; 14,06</t>
+          <t>1,71; 14,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-32,48; 1,05</t>
+          <t>-34,37; 1,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 7,52</t>
+          <t>-4,17; 7,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 3,63</t>
+          <t>-7,75; 4,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-20,69; -6,82</t>
+          <t>-21,61; -7,27</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,85; 9,29</t>
+          <t>0,67; 9,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 6,92</t>
+          <t>-0,89; 7,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-31,2; -5,54</t>
+          <t>-31,65; -5,59</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,97; 33,59</t>
+          <t>4,4; 36,71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,8; 34,05</t>
+          <t>3,73; 34,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-69,56; 2,38</t>
+          <t>-72,21; 3,04</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 12,88</t>
+          <t>-6,39; 12,7</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-12,22; 6,16</t>
+          <t>-12,21; 7,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-32,77; -11,58</t>
+          <t>-33,36; -12,47</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,62; 17,92</t>
+          <t>1,32; 18,58</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 13,56</t>
+          <t>-1,61; 14,03</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-58,34; -10,49</t>
+          <t>-58,19; -10,42</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 6,81</t>
+          <t>-8,46; 6,66</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-11,15; 2,21</t>
+          <t>-11,05; 2,43</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-13,52; -0,54</t>
+          <t>-12,83; -0,42</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,68; 16,79</t>
+          <t>3,64; 16,59</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 9,81</t>
+          <t>-4,3; 9,32</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 3,46</t>
+          <t>-7,61; 3,27</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 9,04</t>
+          <t>-0,54; 9,72</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 4,27</t>
+          <t>-5,35; 4,08</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-8,38; -0,0</t>
+          <t>-8,93; -0,16</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-12,66; 13,16</t>
+          <t>-14,1; 12,9</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-18,93; 4,18</t>
+          <t>-18,67; 4,58</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-23,17; -1,08</t>
+          <t>-21,58; -0,77</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4,8; 31,1</t>
+          <t>5,68; 30,42</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 17,78</t>
+          <t>-6,95; 16,47</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-12,53; 6,2</t>
+          <t>-12,1; 5,93</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 16,57</t>
+          <t>-0,91; 17,82</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 7,83</t>
+          <t>-9,03; 7,34</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-14,01; 0,32</t>
+          <t>-14,85; -0,2</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-12,22; 4,59</t>
+          <t>-11,44; 4,61</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-11,12; 4,15</t>
+          <t>-11,39; 4,1</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-12,73; 1,46</t>
+          <t>-12,54; 1,88</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,52; 14,88</t>
+          <t>-0,09; 15,45</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 9,48</t>
+          <t>-5,54; 9,38</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 30,74</t>
+          <t>-4,33; 34,57</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 8,36</t>
+          <t>-3,13; 7,56</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 4,87</t>
+          <t>-6,27; 4,56</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 24,92</t>
+          <t>-5,15; 24,67</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-20,91; 9,71</t>
+          <t>-19,96; 9,09</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-19,56; 8,29</t>
+          <t>-19,52; 7,87</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-21,29; 2,75</t>
+          <t>-21,22; 3,65</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0,87; 27,72</t>
+          <t>-0,01; 28,6</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 18,24</t>
+          <t>-9,26; 17,47</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 58,59</t>
+          <t>-7,43; 67,71</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 15,97</t>
+          <t>-5,29; 14,21</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-10,26; 9,17</t>
+          <t>-10,78; 8,49</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 48,53</t>
+          <t>-9,16; 46,16</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 12,08</t>
+          <t>-7,12; 11,61</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 8,63</t>
+          <t>-10,18; 8,76</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 8,72</t>
+          <t>-7,93; 8,37</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10,55; 25,27</t>
+          <t>10,07; 25,2</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,84; 18,0</t>
+          <t>2,36; 18,2</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,48; 19,58</t>
+          <t>6,22; 20,05</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,51; 17,65</t>
+          <t>5,51; 17,71</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 12,02</t>
+          <t>-0,09; 12,28</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3,05; 13,3</t>
+          <t>3,65; 13,73</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-11,28; 24,98</t>
+          <t>-11,94; 23,57</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-15,33; 17,49</t>
+          <t>-16,98; 17,85</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-13,28; 17,7</t>
+          <t>-12,98; 17,08</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>19,6; 55,27</t>
+          <t>18,22; 55,95</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>3,39; 38,35</t>
+          <t>4,41; 39,59</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,71; 43,27</t>
+          <t>11,16; 45,33</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>10,16; 36,4</t>
+          <t>10,11; 36,26</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 25,14</t>
+          <t>-0,23; 25,22</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>5,54; 27,24</t>
+          <t>6,34; 28,8</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>3,27; 8,15</t>
+          <t>3,34; 8,3</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2,6; 7,57</t>
+          <t>2,39; 7,51</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-15,06; -0,96</t>
+          <t>-13,71; -0,66</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>5,17; 9,96</t>
+          <t>5,38; 9,88</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 2,95</t>
+          <t>-1,74; 3,26</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 8,24</t>
+          <t>-4,2; 7,91</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>5,04; 8,56</t>
+          <t>5,19; 8,68</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,73</t>
+          <t>1,06; 4,52</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 2,0</t>
+          <t>-7,29; 2,58</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>7,29; 19,58</t>
+          <t>7,57; 19,9</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>5,75; 17,82</t>
+          <t>5,38; 17,95</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-33,67; -2,26</t>
+          <t>-31,02; -1,58</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>9,41; 18,95</t>
+          <t>9,56; 18,62</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 5,59</t>
+          <t>-3,09; 6,15</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 15,27</t>
+          <t>-7,69; 14,62</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>10,18; 17,89</t>
+          <t>10,41; 18,21</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>2,11; 9,93</t>
+          <t>2,11; 9,39</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-14,56; 4,23</t>
+          <t>-14,96; 5,36</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/MCS12_SP_R2-Edad-trans_camb.xlsx
+++ b/data/trans_camb/MCS12_SP_R2-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-6,5</t>
+          <t>-2,99</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-3,76</t>
+          <t>-5,65</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-5,81</t>
+          <t>-4,42</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 8,81</t>
+          <t>-2,71; 8,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 8,02</t>
+          <t>-5,21; 7,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,83; 2,79</t>
+          <t>-11,22; 5,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 13,09</t>
+          <t>-0,34; 13,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 7,29</t>
+          <t>-5,17; 7,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,18; 4,64</t>
+          <t>-14,01; 2,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,11; 9,06</t>
+          <t>0,12; 9,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 5,54</t>
+          <t>-3,44; 5,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-12,43; 0,58</t>
+          <t>-10,6; 1,47</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-20,12%</t>
+          <t>-9,25%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-8,76%</t>
+          <t>-13,17%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-15,51%</t>
+          <t>-11,79%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 29,92</t>
+          <t>-7,83; 31,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,67; 26,62</t>
+          <t>-14,64; 27,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-43,9; 9,32</t>
+          <t>-31,95; 18,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 32,5</t>
+          <t>-0,73; 32,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-13,89; 18,46</t>
+          <t>-11,61; 18,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-27,69; 11,32</t>
+          <t>-30,84; 5,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 26,05</t>
+          <t>0,33; 26,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-9,44; 15,78</t>
+          <t>-8,83; 15,68</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-31,78; 1,67</t>
+          <t>-27,41; 4,53</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,59</t>
+          <t>-0,23</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,85</t>
+          <t>-8,17</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,5</t>
+          <t>-3,55</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,91; 15,28</t>
+          <t>4,74; 15,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,67; 16,85</t>
+          <t>5,92; 16,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 5,81</t>
+          <t>-6,55; 5,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 12,81</t>
+          <t>0,71; 12,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 6,61</t>
+          <t>-5,23; 6,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,33; 18,92</t>
+          <t>-14,04; -2,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,7; 12,36</t>
+          <t>4,93; 12,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,71; 10,62</t>
+          <t>2,75; 10,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 15,93</t>
+          <t>-7,68; 1,11</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-1,71%</t>
+          <t>-0,67%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-1,76%</t>
+          <t>-16,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>-8,68%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,6; 47,51</t>
+          <t>12,67; 46,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,72; 53,23</t>
+          <t>15,08; 52,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-21,79; 18,04</t>
+          <t>-18,63; 18,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,08; 28,5</t>
+          <t>1,37; 27,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 14,37</t>
+          <t>-10,05; 14,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-23,02; 39,61</t>
+          <t>-27,75; -4,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,07; 31,34</t>
+          <t>11,42; 31,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,23; 26,9</t>
+          <t>6,45; 26,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-14,17; 40,16</t>
+          <t>-18,5; 2,78</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-7,53</t>
+          <t>-7,5</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-14,12</t>
+          <t>-12,72</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-11,08</t>
+          <t>-10,39</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,38; 12,74</t>
+          <t>1,9; 12,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 9,58</t>
+          <t>-1,32; 9,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,85; -1,71</t>
+          <t>-12,97; -2,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,3; 10,76</t>
+          <t>0,31; 10,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,31; -3,35</t>
+          <t>-14,21; -3,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-19,65; -9,15</t>
+          <t>-17,62; -7,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,37; 10,3</t>
+          <t>2,26; 10,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 1,56</t>
+          <t>-6,36; 1,5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-14,89; -7,04</t>
+          <t>-14,14; -6,64</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-17,26%</t>
+          <t>-17,18%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-24,28%</t>
+          <t>-21,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-21,65%</t>
+          <t>-20,29%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,98; 32,05</t>
+          <t>4,12; 31,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 23,67</t>
+          <t>-2,78; 24,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-28,43; -4,48</t>
+          <t>-28,17; -5,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,46; 19,52</t>
+          <t>0,46; 19,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-23,57; -5,95</t>
+          <t>-23,1; -5,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-31,76; -16,08</t>
+          <t>-28,95; -13,96</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,25; 20,89</t>
+          <t>4,32; 20,84</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-11,6; 3,17</t>
+          <t>-11,96; 3,08</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-28,01; -14,28</t>
+          <t>-26,72; -13,53</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-13,2</t>
+          <t>-1,83</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-12,68</t>
+          <t>-10,46</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-13,89</t>
+          <t>-6,01</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,06; 15,11</t>
+          <t>2,27; 15,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,71; 14,24</t>
+          <t>1,39; 13,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-34,37; 1,36</t>
+          <t>-7,82; 3,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 7,44</t>
+          <t>-4,22; 6,84</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 4,35</t>
+          <t>-7,73; 3,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-21,61; -7,27</t>
+          <t>-15,81; -5,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,67; 9,57</t>
+          <t>0,34; 9,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 7,24</t>
+          <t>-1,47; 7,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-31,65; -5,59</t>
+          <t>-10,0; -2,06</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-29,17%</t>
+          <t>-4,03%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-20,3%</t>
+          <t>-16,74%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-25,8%</t>
+          <t>-11,16%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,4; 36,71</t>
+          <t>4,9; 36,54</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,73; 34,67</t>
+          <t>2,79; 33,16</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-72,21; 3,04</t>
+          <t>-15,92; 9,16</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 12,7</t>
+          <t>-6,67; 11,66</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-12,21; 7,33</t>
+          <t>-11,71; 5,85</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-33,36; -12,47</t>
+          <t>-23,97; -9,22</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,32; 18,58</t>
+          <t>0,6; 18,47</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 14,03</t>
+          <t>-2,64; 14,14</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-58,19; -10,42</t>
+          <t>-17,85; -4,05</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-6,68</t>
+          <t>-7,08</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-2,04</t>
+          <t>-1,17</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-4,42</t>
+          <t>-4,14</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 6,66</t>
+          <t>-8,46; 5,32</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-11,05; 2,43</t>
+          <t>-11,19; 3,4</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-12,83; -0,42</t>
+          <t>-13,14; -0,84</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,64; 16,59</t>
+          <t>3,05; 16,23</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 9,32</t>
+          <t>-4,18; 8,95</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 3,27</t>
+          <t>-6,57; 4,93</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 9,72</t>
+          <t>-0,38; 9,33</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 4,08</t>
+          <t>-5,96; 3,8</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-8,93; -0,16</t>
+          <t>-8,69; -0,12</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-11,93%</t>
+          <t>-12,66%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-3,45%</t>
+          <t>-1,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-7,69%</t>
+          <t>-7,21%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-14,1; 12,9</t>
+          <t>-14,36; 10,03</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-18,67; 4,58</t>
+          <t>-18,78; 6,67</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-21,58; -0,77</t>
+          <t>-22,22; -1,72</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5,68; 30,42</t>
+          <t>4,68; 29,76</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 16,47</t>
+          <t>-6,55; 16,29</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-12,1; 5,93</t>
+          <t>-10,58; 9,18</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 17,82</t>
+          <t>-0,62; 17,18</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 7,34</t>
+          <t>-9,84; 6,89</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-14,85; -0,2</t>
+          <t>-14,23; 0,01</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-5,13</t>
+          <t>-5,56</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,03</t>
+          <t>-1,2</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>6,48</t>
+          <t>-3,34</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-11,44; 4,61</t>
+          <t>-11,66; 4,56</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-11,39; 4,1</t>
+          <t>-11,44; 4,4</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-12,54; 1,88</t>
+          <t>-12,56; 1,42</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 15,45</t>
+          <t>0,18; 15,51</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 9,38</t>
+          <t>-5,93; 8,61</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 34,57</t>
+          <t>-6,64; 4,96</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 7,56</t>
+          <t>-3,32; 7,75</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 4,56</t>
+          <t>-6,16; 4,0</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 24,67</t>
+          <t>-8,07; 1,19</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-9,48%</t>
+          <t>-10,27%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>-2,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>-6,0%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-19,96; 9,09</t>
+          <t>-20,5; 8,97</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-19,52; 7,87</t>
+          <t>-19,71; 9,01</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-21,22; 3,65</t>
+          <t>-21,62; 2,42</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 28,6</t>
+          <t>0,63; 29,39</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 17,47</t>
+          <t>-9,78; 16,14</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 67,71</t>
+          <t>-10,89; 9,32</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 14,21</t>
+          <t>-5,37; 14,51</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-10,78; 8,49</t>
+          <t>-10,73; 7,49</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-9,16; 46,16</t>
+          <t>-13,72; 2,23</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0,62</t>
+          <t>1,01</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,23</t>
+          <t>13,17</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>8,23</t>
+          <t>8,34</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 11,61</t>
+          <t>-7,03; 12,42</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-10,18; 8,76</t>
+          <t>-10,18; 7,52</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-7,93; 8,37</t>
+          <t>-7,53; 8,95</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10,07; 25,2</t>
+          <t>10,6; 24,93</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,36; 18,2</t>
+          <t>1,5; 17,09</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,22; 20,05</t>
+          <t>6,24; 20,02</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,51; 17,71</t>
+          <t>5,98; 17,86</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 12,28</t>
+          <t>0,06; 12,06</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3,65; 13,73</t>
+          <t>3,21; 13,51</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,0%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-11,94; 23,57</t>
+          <t>-11,73; 25,41</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-16,98; 17,85</t>
+          <t>-16,87; 15,01</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-12,98; 17,08</t>
+          <t>-12,85; 17,95</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>18,22; 55,95</t>
+          <t>19,08; 54,66</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>4,41; 39,59</t>
+          <t>3,19; 37,79</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,16; 45,33</t>
+          <t>11,14; 44,6</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>10,11; 36,26</t>
+          <t>10,7; 36,66</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 25,22</t>
+          <t>0,1; 24,6</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>6,34; 28,8</t>
+          <t>5,81; 28,42</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-4,58</t>
+          <t>-1,37</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-0,38</t>
+          <t>-3,42</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-2,35</t>
+          <t>-2,36</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>3,34; 8,3</t>
+          <t>3,3; 8,39</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2,39; 7,51</t>
+          <t>2,48; 7,36</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-13,71; -0,66</t>
+          <t>-3,87; 1,18</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>5,38; 9,88</t>
+          <t>5,52; 10,23</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 3,26</t>
+          <t>-1,98; 2,89</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 7,91</t>
+          <t>-5,84; -1,08</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>5,19; 8,68</t>
+          <t>4,82; 8,34</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,52</t>
+          <t>0,94; 4,42</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 2,58</t>
+          <t>-4,17; -0,77</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-10,6%</t>
+          <t>-3,18%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-0,7%</t>
+          <t>-6,31%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-4,82%</t>
+          <t>-4,83%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>7,57; 19,9</t>
+          <t>7,34; 19,86</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>5,38; 17,95</t>
+          <t>5,5; 17,51</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-31,02; -1,58</t>
+          <t>-8,77; 2,78</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>9,56; 18,62</t>
+          <t>9,96; 19,25</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 6,15</t>
+          <t>-3,57; 5,5</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 14,62</t>
+          <t>-10,48; -2,0</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>10,41; 18,21</t>
+          <t>9,69; 17,42</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>2,11; 9,39</t>
+          <t>1,87; 9,22</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-14,96; 5,36</t>
+          <t>-8,37; -1,58</t>
         </is>
       </c>
     </row>
